--- a/test-design/Test_Case_Design_Sheet.xlsx
+++ b/test-design/Test_Case_Design_Sheet.xlsx
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">RUN-3: API-V01 (with key) and API-V02 (without) both returned 404. curl on 28 Oct: http://34.93.84.61:8000/api/products = connection timed out (not reachable from the tester machine); :8081/api/products and :8082/api/products = HTTP 404 with a Laravel "Not Found" HTML page (Apache/PHP) - the server is up but has no route at that path.</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFIRMED: /api/products does not exist on :8081 or :8082, and :8000 is not reachable. NOT YET KNOWN: where the API really is (different prefix such as /api/v1, or an API only enabled on a local server). npm run discover:api records the calls the app's own pages make and probes likely paths.</t>
+    <t xml:space="preserve">CONFIRMED (discover:api, 28 Oct): all 24 probed paths under /api, /api/v1, /index.php/api, /public/api, /insurance/api and /api/insurance returned 404 on :8081; the pages make no background API calls and contain no /api strings. Anonymous GET /products and /applications return 401 JSON, which looks like the app's own login-protected pages, not a key-protected API. /health and /riders are 404. CONFIRMED: /api/products does not exist on :8081 or :8082, and :8000 is not reachable from the tester machine (possibly open only on the VM itself). NOT YET KNOWN: where the API really is (different prefix such as /api/v1, or an API only enabled on a local server). npm run discover:api records the calls the app's own pages make and probes likely paths.</t>
   </si>
   <si>
     <t xml:space="preserve">Open - real API path not yet found (run npm run discover:api)</t>
   </si>
   <si>
-    <t xml:space="preserve">scripts/discover-api.js; then set INSURANCE_API_URL (or adjust config/endpoints.js)</t>
+    <t xml:space="preserve">API tests now SKIP as an environment issue until the API answers (API_REQUIRED=true makes it a failure); ask the lab for the API address or run the API tests on the VM / via an SSH tunnel to :8000</t>
   </si>
   <si>
     <t xml:space="preserve">Review / Validation</t>
@@ -18094,7 +18094,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>1246</v>
       </c>
